--- a/server/protected-digital-products/excel/personal-budget-system.xlsx
+++ b/server/protected-digital-products/excel/personal-budget-system.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rdcbf63b8351c4fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="Rb4df4b9ef32d4069"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income" sheetId="3" r:id="Rb2ba2120dfd34c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="4" r:id="Rcddb5dbc729f4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Savings Goals" sheetId="5" r:id="R48e26a39d98d459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Review" sheetId="6" r:id="R7d50d3001174437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="7" r:id="Rb285efe16e2c4838"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R43784cd7b778493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" r:id="R6bc33d2bd35b4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income" sheetId="3" r:id="R2e07d3d582d54142"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="4" r:id="R67ac5b37c75d41a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Savings Goals" sheetId="5" r:id="R306108330b62408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Summary" sheetId="6" r:id="R3f41b92918f84086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Review" sheetId="7" r:id="R4173abe440ff4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="8" r:id="R901f969af11a4ade"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,13 +20,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="0%"/>
     <x:numFmt numFmtId="201" formatCode="#,##0"/>
     <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="203" formatCode="0.0%"/>
+    <x:numFmt numFmtId="204" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,12 +45,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="1D5443"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:sz val="11"/>
       <x:color rgb="071310"/>
       <x:name val="Carlito"/>
@@ -60,14 +56,14 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="1F2A24"/>
+      <x:color rgb="1D5443"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="17382E"/>
+      <x:color rgb="17211C"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -90,12 +86,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FBF8EF"/>
+        <x:fgColor rgb="1D5443"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1D5443"/>
+        <x:fgColor rgb="E7F4EA"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -105,7 +101,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="E7F4EA"/>
+        <x:fgColor rgb="FBF8EF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -115,7 +111,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="44">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -132,7 +128,6 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
@@ -143,85 +138,83 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="204" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="203" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -392,13 +385,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -412,7 +405,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra88412d73cdc43fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c5ccec370d8412d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -571,153 +564,177 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28.940000534057617" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34.31999969482422" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="35.66999816894531" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30.280000686645508" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20.860000610351562" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20.860000610351562" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="20.860000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20.860000610351562" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="B1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="E1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="F1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
       <x:c r="G1" s="5" t="str">
-        <x:v>Personal Budget System</x:v>
+        <x:v>Personal Budget System V16</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="str">
+        <x:v>Personal Budget System V16</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Asmeninio biudžeto valdymo sistema su PDF gidu ir Excel modeliu.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="8" t="str">
-        <x:v>Kaip pradėti</x:v>
-      </x:c>
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Asmeninio biudžeto sistema su PDF gidu ir Excel modeliu.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="13" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="str">
+        <x:v>Įveskite savo duomenis tik pažymėtuose įvesties laukeliuose.</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="str">
+        <x:v>Spalvų gidas</x:v>
+      </x:c>
+      <x:c r="E5" s="17" t="str"/>
+      <x:c r="F5" s="17" t="str"/>
+      <x:c r="G5" s="17" t="str"/>
+      <x:c r="H5" s="17" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>Įveskite savo mėnesį, valiutą ir taupymo tikslą Inputs lape.</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str">
-        <x:v>Svarbu</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="str"/>
-      <x:c r="F6" s="16" t="str"/>
-      <x:c r="G6" s="16" t="str"/>
+      <x:c r="A6" s="13" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="str">
+        <x:v>Nelieskite formulių laukelių, jeigu nenorite pakeisti skaičiavimų.</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="str">
+        <x:v>Geltoni langeliai</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="str">
+        <x:v>Įvestys, kurias galite keisti</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="str"/>
+      <x:c r="G6" s="19" t="str"/>
+      <x:c r="H6" s="19" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="14" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>Income lape pakeiskite pavyzdines pajamas savais skaičiais.</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="str">
-        <x:v>Įvesties langeliai pažymėti švelnia geltona spalva.</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="str"/>
-      <x:c r="F7" s="16" t="str"/>
-      <x:c r="G7" s="16" t="str"/>
+      <x:c r="A7" s="13" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="str">
+        <x:v>Pajamų ir išlaidų duomenys automatiškai atsispindi Dashboard lape.</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="str">
+        <x:v>Žali langeliai</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="str">
+        <x:v>Formulės ir automatiniai rezultatai</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="str"/>
+      <x:c r="G7" s="19" t="str"/>
+      <x:c r="H7" s="19" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="14" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="str">
-        <x:v>Expenses lape suveskite planuotas ir realias išlaidas pagal kategorijas.</x:v>
-      </x:c>
-      <x:c r="D8" s="16" t="str">
-        <x:v>Formulių ir rezultatų langeliai pažymėti žalia spalva.</x:v>
-      </x:c>
-      <x:c r="E8" s="16" t="str"/>
-      <x:c r="F8" s="16" t="str"/>
-      <x:c r="G8" s="16" t="str"/>
+      <x:c r="A8" s="13" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="str">
+        <x:v>Kiekvieną mėnesį atnaujinkite duomenis ir atlikite Monthly Review.</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="str">
+        <x:v>Tamsūs langeliai</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="str">
+        <x:v>Antraštės ir struktūros ženklai</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="str"/>
+      <x:c r="G8" s="19" t="str"/>
+      <x:c r="H8" s="19" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="14" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>Savings Goals lape įveskite tikslus ir jau sukauptas sumas.</x:v>
-      </x:c>
-      <x:c r="D9" s="16" t="str">
-        <x:v>Neredaguokite formulių, jei norite išlaikyti automatinį dashboard.</x:v>
-      </x:c>
-      <x:c r="E9" s="16" t="str"/>
-      <x:c r="F9" s="16" t="str"/>
-      <x:c r="G9" s="16" t="str"/>
+      <x:c r="A9" s="13" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="10" t="str">
+        <x:v>Šis failas neturi makrokomandų ir neveikia su išoriniais duomenų šaltiniais.</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="str">
+        <x:v>V16 dashboard</x:v>
+      </x:c>
+      <x:c r="E9" s="19" t="str">
+        <x:v>Rodikliai, sveikatos balas ir rekomendacijos</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="str"/>
+      <x:c r="G9" s="19" t="str"/>
+      <x:c r="H9" s="19" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="14" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>Monthly Review lape užrašykite įžvalgas ir kitus veiksmus.</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="str">
-        <x:v>Failą atnaujinkite kiekvieną mėnesį arba susikurkite kopiją naujam mėnesiui.</x:v>
-      </x:c>
-      <x:c r="E10" s="16" t="str"/>
-      <x:c r="F10" s="16" t="str"/>
-      <x:c r="G10" s="16" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="14" t="str">
+      <x:c r="A10" s="13" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>Dashboard lape matysite automatinius rezultatus ir rekomendaciją.</x:v>
-      </x:c>
+      <x:c r="B10" s="10" t="str">
+        <x:v>Naudokite Category Summary lapą kategorijų analizei ir optimizavimui.</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="str">
+        <x:v>Ritmas</x:v>
+      </x:c>
+      <x:c r="E10" s="19" t="str">
+        <x:v>Pildyti kas savaitę, peržiūrėti mėnesio pabaigoje</x:v>
+      </x:c>
+      <x:c r="F10" s="19" t="str"/>
+      <x:c r="G10" s="19" t="str"/>
+      <x:c r="H10" s="19" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
-    <x:mergeCell ref="A4:G4"/>
-    <x:mergeCell ref="D6:G6"/>
-    <x:mergeCell ref="D7:G7"/>
-    <x:mergeCell ref="D8:G8"/>
-    <x:mergeCell ref="D9:G9"/>
-    <x:mergeCell ref="D10:G10"/>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:H2"/>
+    <x:mergeCell ref="D5:H5"/>
+    <x:mergeCell ref="E6:H6"/>
+    <x:mergeCell ref="E7:H7"/>
+    <x:mergeCell ref="E8:H8"/>
+    <x:mergeCell ref="E9:H9"/>
+    <x:mergeCell ref="E10:H10"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -727,11 +744,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="27.59000015258789" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.940000534057617" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30.280000686645508" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="31.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="55.849998474121094" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18.170000076293945" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.170000076293945" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -750,100 +768,117 @@
       <x:c r="E1" s="5" t="str">
         <x:v>Inputs</x:v>
       </x:c>
+      <x:c r="F1" s="5" t="str">
+        <x:v>Inputs</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Pagrindiniai mėnesio nustatymai ir pastabos.</x:v>
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Mėnesio nustatymai, tikslai ir kontekstas.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24" t="str">
-        <x:v>Laukas</x:v>
-      </x:c>
-      <x:c r="B4" s="24" t="str">
-        <x:v>Įvestis</x:v>
-      </x:c>
-      <x:c r="C4" s="24" t="str">
-        <x:v>Pastaba</x:v>
+      <x:c r="A4" s="16" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Input</x:v>
+      </x:c>
+      <x:c r="C4" s="16" t="str">
+        <x:v>Note</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Mėnuo</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
+      <x:c r="A5" s="10" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
         <x:v>2026 gegužė</x:v>
       </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>Įrašykite mėnesį, kuriam pildomas biudžetas.</x:v>
+      <x:c r="C5" s="10" t="str">
+        <x:v>Mėnuo, kuriam pildomas modelis.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Valiuta</x:v>
-      </x:c>
-      <x:c r="B6" s="26" t="str">
+      <x:c r="A6" s="10" t="str">
+        <x:v>Currency</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
         <x:v>€</x:v>
       </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Naudojama visame modelyje.</x:v>
+      <x:c r="C6" s="10" t="str">
+        <x:v>Naudojama vizualiai dashboard ir lentelėse.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>Taupymo tikslas %</x:v>
-      </x:c>
-      <x:c r="B7" s="27" t="n">
+      <x:c r="A7" s="10" t="str">
+        <x:v>User / household name</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>StillOak šeima</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="str">
+        <x:v>Asmuo arba namų ūkis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>Savings target %</x:v>
+      </x:c>
+      <x:c r="B8" s="26" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str">
+      <x:c r="C8" s="10" t="str">
         <x:v>Pageidaujama mėnesio taupymo norma.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>Emergency fund goal</x:v>
-      </x:c>
-      <x:c r="B8" s="28" t="n">
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>Emergency fund target</x:v>
+      </x:c>
+      <x:c r="B9" s="27" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>Tikslinė saugumo rezervo suma.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Mėnesio pastabos</x:v>
-      </x:c>
-      <x:c r="B9" s="26" t="str">
-        <x:v>Pavyzdinis mėnuo su nuoma, maistu, transportu ir taupymu.</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>Trumpas kontekstas peržiūrai.</x:v>
+      <x:c r="C9" s="10" t="str">
+        <x:v>Saugumo rezervo tikslas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>Monthly note</x:v>
+      </x:c>
+      <x:c r="B10" s="25" t="str">
+        <x:v>Pavyzdinis mėnuo su papildomomis pajamomis ir keliomis optional išlaidomis.</x:v>
+      </x:c>
+      <x:c r="C10" s="10" t="str">
+        <x:v>Trumpa pastaba mėnesio peržiūrai.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -854,15 +889,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="14.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26.239999771118164" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27.59000015258789" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20.860000610351562" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="19.520000457763672" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.520000457763672" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16.81999969482422" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="34.31999969482422" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="3.359999895095825" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22.209999084472656" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="19.520000457763672" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -890,278 +922,316 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Planuotos ir realios mėnesio pajamos.</x:v>
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Pajamų planas, realūs skaičiai ir nukrypimai.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="24" t="str">
+      <x:c r="A5" s="16" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B5" s="24" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>Income Source</x:v>
       </x:c>
-      <x:c r="C5" s="24" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>Category</x:v>
       </x:c>
-      <x:c r="D5" s="24" t="str">
+      <x:c r="D5" s="16" t="str">
         <x:v>Planned Income</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str">
+      <x:c r="E5" s="16" t="str">
         <x:v>Actual Income</x:v>
       </x:c>
-      <x:c r="F5" s="24" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>Difference</x:v>
       </x:c>
-      <x:c r="G5" s="24" t="str">
+      <x:c r="G5" s="16" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="31" t="n">
+      <x:c r="A6" s="28" t="n">
         <x:v>46143</x:v>
       </x:c>
-      <x:c r="B6" s="26" t="str">
+      <x:c r="B6" s="25" t="str">
         <x:v>Pagrindinis atlyginimas</x:v>
       </x:c>
-      <x:c r="C6" s="26" t="str">
+      <x:c r="C6" s="25" t="str">
         <x:v>Salary</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="n">
+      <x:c r="D6" s="27" t="n">
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="E6" s="28" t="n">
+      <x:c r="E6" s="27" t="n">
         <x:v>2400</x:v>
       </x:c>
-      <x:c r="F6" s="32" t="n">
+      <x:c r="F6" s="29" t="n">
         <x:f>E6-D6</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="26" t="str">
+      <x:c r="G6" s="25" t="str">
         <x:v>Reguliarios pajamos</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="31" t="n">
+      <x:c r="A7" s="28" t="n">
         <x:v>46147</x:v>
       </x:c>
-      <x:c r="B7" s="26" t="str">
+      <x:c r="B7" s="25" t="str">
         <x:v>Freelance projektas</x:v>
       </x:c>
-      <x:c r="C7" s="26" t="str">
+      <x:c r="C7" s="25" t="str">
         <x:v>Freelance</x:v>
       </x:c>
-      <x:c r="D7" s="28" t="n">
+      <x:c r="D7" s="27" t="n">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="E7" s="28" t="n">
+      <x:c r="E7" s="27" t="n">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="F7" s="32" t="n">
+      <x:c r="F7" s="29" t="n">
         <x:f>E7-D7</x:f>
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="str">
+      <x:c r="G7" s="25" t="str">
         <x:v>Papildomas darbas</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="31" t="n">
+      <x:c r="A8" s="28" t="n">
         <x:v>46154</x:v>
       </x:c>
-      <x:c r="B8" s="26" t="str">
+      <x:c r="B8" s="25" t="str">
         <x:v>Skaitmeninis produktas</x:v>
       </x:c>
-      <x:c r="C8" s="26" t="str">
+      <x:c r="C8" s="25" t="str">
         <x:v>Side income</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="n">
+      <x:c r="D8" s="27" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E8" s="28" t="n">
+      <x:c r="E8" s="27" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="n">
+      <x:c r="F8" s="29" t="n">
         <x:f>E8-D8</x:f>
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G8" s="26" t="str">
+      <x:c r="G8" s="25" t="str">
         <x:v>Papildomos pajamos</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="31" t="n">
+      <x:c r="A9" s="28" t="n">
         <x:v>46162</x:v>
       </x:c>
-      <x:c r="B9" s="26" t="str">
+      <x:c r="B9" s="25" t="str">
         <x:v>Grąžinimas</x:v>
       </x:c>
-      <x:c r="C9" s="26" t="str">
+      <x:c r="C9" s="25" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="n">
+      <x:c r="D9" s="27" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="n">
+      <x:c r="E9" s="27" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="F9" s="32" t="n">
+      <x:c r="F9" s="29" t="n">
         <x:f>E9-D9</x:f>
         <x:v>-15</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="str">
+      <x:c r="G9" s="25" t="str">
         <x:v>Vienkartinė suma</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="31"/>
-      <x:c r="B10" s="26" t="str"/>
-      <x:c r="C10" s="26" t="str"/>
-      <x:c r="D10" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
+      <x:c r="A10" s="28"/>
+      <x:c r="B10" s="25" t="str"/>
+      <x:c r="C10" s="25" t="str"/>
+      <x:c r="D10" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="29" t="n">
         <x:f>E10-D10</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="str"/>
+      <x:c r="G10" s="25" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="31"/>
-      <x:c r="B11" s="26" t="str"/>
-      <x:c r="C11" s="26" t="str"/>
-      <x:c r="D11" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
+      <x:c r="A11" s="28"/>
+      <x:c r="B11" s="25" t="str"/>
+      <x:c r="C11" s="25" t="str"/>
+      <x:c r="D11" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="29" t="n">
         <x:f>E11-D11</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="str"/>
+      <x:c r="G11" s="25" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="31"/>
-      <x:c r="B12" s="26" t="str"/>
-      <x:c r="C12" s="26" t="str"/>
-      <x:c r="D12" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="A12" s="28"/>
+      <x:c r="B12" s="25" t="str"/>
+      <x:c r="C12" s="25" t="str"/>
+      <x:c r="D12" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="29" t="n">
         <x:f>E12-D12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="26" t="str"/>
+      <x:c r="G12" s="25" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="31"/>
-      <x:c r="B13" s="26" t="str"/>
-      <x:c r="C13" s="26" t="str"/>
-      <x:c r="D13" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
+      <x:c r="A13" s="28"/>
+      <x:c r="B13" s="25" t="str"/>
+      <x:c r="C13" s="25" t="str"/>
+      <x:c r="D13" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="29" t="n">
         <x:f>E13-D13</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="str"/>
+      <x:c r="G13" s="25" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="31"/>
-      <x:c r="B14" s="26" t="str"/>
-      <x:c r="C14" s="26" t="str"/>
-      <x:c r="D14" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E14" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="A14" s="28"/>
+      <x:c r="B14" s="25" t="str"/>
+      <x:c r="C14" s="25" t="str"/>
+      <x:c r="D14" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="29" t="n">
         <x:f>E14-D14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="26" t="str"/>
+      <x:c r="G14" s="25" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="31"/>
-      <x:c r="B15" s="26" t="str"/>
-      <x:c r="C15" s="26" t="str"/>
-      <x:c r="D15" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E15" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
+      <x:c r="A15" s="28"/>
+      <x:c r="B15" s="25" t="str"/>
+      <x:c r="C15" s="25" t="str"/>
+      <x:c r="D15" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="29" t="n">
         <x:f>E15-D15</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="str"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="23" t="str">
+      <x:c r="G15" s="25" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="28"/>
+      <x:c r="B16" s="25" t="str"/>
+      <x:c r="C16" s="25" t="str"/>
+      <x:c r="D16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="29" t="n">
+        <x:f>E16-D16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="25" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="28"/>
+      <x:c r="B17" s="25" t="str"/>
+      <x:c r="C17" s="25" t="str"/>
+      <x:c r="D17" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="n">
+        <x:f>E17-D17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="25" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="17" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="B18" s="23" t="str"/>
-      <x:c r="C18" s="23" t="str"/>
-      <x:c r="D18" s="37" t="n">
-        <x:f>SUM(D6:D15)</x:f>
+      <x:c r="B20" s="17" t="str"/>
+      <x:c r="C20" s="17" t="str"/>
+      <x:c r="D20" s="17" t="str">
+        <x:v>Total planned income</x:v>
+      </x:c>
+      <x:c r="E20" s="17" t="str">
+        <x:v>Total actual income</x:v>
+      </x:c>
+      <x:c r="F20" s="17" t="str">
+        <x:v>Income variance %</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" s="33" t="n">
+        <x:f>SUM(D6:D17)</x:f>
         <x:v>2920</x:v>
       </x:c>
-      <x:c r="E18" s="37" t="n">
-        <x:f>SUM(E6:E15)</x:f>
+      <x:c r="E21" s="33" t="n">
+        <x:f>SUM(E6:E17)</x:f>
         <x:v>3015</x:v>
       </x:c>
-      <x:c r="F18" s="37" t="n">
-        <x:f>E18-D18</x:f>
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="str">
-        <x:v>Income variance %</x:v>
-      </x:c>
-      <x:c r="B19" t="str"/>
-      <x:c r="C19" t="str"/>
-      <x:c r="D19" s="36" t="str"/>
-      <x:c r="E19" s="36" t="str"/>
-      <x:c r="F19" s="38" t="n">
-        <x:f>IFERROR(F18/D18,0)</x:f>
+      <x:c r="F21" s="34" t="n">
+        <x:f>IFERROR((E21-D21)/D21,0)</x:f>
         <x:v>0.032534246575342464</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1173,15 +1243,12 @@
   <x:cols>
     <x:col min="1" max="1" width="14.130000114440918" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="22.209999084472656" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28.940000534057617" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30.280000686645508" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="19.520000457763672" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.520000457763672" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16.81999969482422" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.860000610351562" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="31.6299991607666" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="3.359999895095825" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="23.549999237060547" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="19.520000457763672" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1212,638 +1279,599 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Planuotos ir realios išlaidos pagal kategorijas.</x:v>
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Išlaidų planas, realūs skaičiai ir būtinybės lygis.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="24" t="str">
+      <x:c r="A5" s="16" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B5" s="24" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>Expense Category</x:v>
       </x:c>
-      <x:c r="C5" s="24" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>Description</x:v>
       </x:c>
-      <x:c r="D5" s="24" t="str">
+      <x:c r="D5" s="16" t="str">
         <x:v>Planned Expense</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str">
+      <x:c r="E5" s="16" t="str">
         <x:v>Actual Expense</x:v>
       </x:c>
-      <x:c r="F5" s="24" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>Difference</x:v>
       </x:c>
-      <x:c r="G5" s="24" t="str">
-        <x:v>Essential / Optional</x:v>
-      </x:c>
-      <x:c r="H5" s="24" t="str">
+      <x:c r="G5" s="16" t="str">
+        <x:v>Type</x:v>
+      </x:c>
+      <x:c r="H5" s="16" t="str">
         <x:v>Notes</x:v>
       </x:c>
-      <x:c r="J5" s="24" t="str">
-        <x:v>Category</x:v>
-      </x:c>
-      <x:c r="K5" s="24" t="str">
-        <x:v>Actual Total</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="31" t="n">
+      <x:c r="A6" s="28" t="n">
         <x:v>46144</x:v>
       </x:c>
-      <x:c r="B6" s="26" t="str">
+      <x:c r="B6" s="25" t="str">
         <x:v>Housing</x:v>
       </x:c>
-      <x:c r="C6" s="26" t="str">
+      <x:c r="C6" s="25" t="str">
         <x:v>Nuoma</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="n">
+      <x:c r="D6" s="27" t="n">
         <x:v>850</x:v>
       </x:c>
-      <x:c r="E6" s="28" t="n">
+      <x:c r="E6" s="27" t="n">
         <x:v>850</x:v>
       </x:c>
-      <x:c r="F6" s="32" t="n">
+      <x:c r="F6" s="29" t="n">
         <x:f>D6-E6</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="26" t="str">
+      <x:c r="G6" s="25" t="str">
         <x:v>Essential</x:v>
       </x:c>
-      <x:c r="H6" s="26" t="str">
+      <x:c r="H6" s="25" t="str">
         <x:v>Pastovi išlaida</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>Housing</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J6,$E$6:$E$25)</x:f>
-        <x:v>850</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="31" t="n">
+      <x:c r="A7" s="28" t="n">
         <x:v>46145</x:v>
       </x:c>
-      <x:c r="B7" s="26" t="str">
+      <x:c r="B7" s="25" t="str">
         <x:v>Food</x:v>
       </x:c>
-      <x:c r="C7" s="26" t="str">
+      <x:c r="C7" s="25" t="str">
         <x:v>Maisto produktai</x:v>
       </x:c>
-      <x:c r="D7" s="28" t="n">
+      <x:c r="D7" s="27" t="n">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="E7" s="28" t="n">
+      <x:c r="E7" s="27" t="n">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="F7" s="32" t="n">
+      <x:c r="F7" s="29" t="n">
         <x:f>D7-E7</x:f>
         <x:v>-35</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="str">
+      <x:c r="G7" s="25" t="str">
         <x:v>Essential</x:v>
       </x:c>
-      <x:c r="H7" s="26" t="str">
+      <x:c r="H7" s="25" t="str">
         <x:v>Šiek tiek virš plano</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="str">
-        <x:v>Food</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J7,$E$6:$E$25)</x:f>
-        <x:v>455</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="31" t="n">
+      <x:c r="A8" s="28" t="n">
         <x:v>46146</x:v>
       </x:c>
-      <x:c r="B8" s="26" t="str">
+      <x:c r="B8" s="25" t="str">
         <x:v>Transport</x:v>
       </x:c>
-      <x:c r="C8" s="26" t="str">
+      <x:c r="C8" s="25" t="str">
         <x:v>Kuras ir viešasis transportas</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="n">
+      <x:c r="D8" s="27" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E8" s="28" t="n">
+      <x:c r="E8" s="27" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F8" s="32" t="n">
+      <x:c r="F8" s="29" t="n">
         <x:f>D8-E8</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G8" s="26" t="str">
+      <x:c r="G8" s="25" t="str">
         <x:v>Essential</x:v>
       </x:c>
-      <x:c r="H8" s="26" t="str"/>
-      <x:c r="J8" s="11" t="str">
-        <x:v>Transport</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J8,$E$6:$E$25)</x:f>
-        <x:v>110</x:v>
-      </x:c>
+      <x:c r="H8" s="25" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="31" t="n">
+      <x:c r="A9" s="28" t="n">
         <x:v>46147</x:v>
       </x:c>
-      <x:c r="B9" s="26" t="str">
+      <x:c r="B9" s="25" t="str">
         <x:v>Utilities</x:v>
       </x:c>
-      <x:c r="C9" s="26" t="str">
+      <x:c r="C9" s="25" t="str">
         <x:v>Elektra, vanduo, internetas</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="n">
+      <x:c r="D9" s="27" t="n">
         <x:v>160</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="n">
+      <x:c r="E9" s="27" t="n">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="F9" s="32" t="n">
+      <x:c r="F9" s="29" t="n">
         <x:f>D9-E9</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="str">
+      <x:c r="G9" s="25" t="str">
         <x:v>Essential</x:v>
       </x:c>
-      <x:c r="H9" s="26" t="str"/>
-      <x:c r="J9" s="11" t="str">
-        <x:v>Utilities</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J9,$E$6:$E$25)</x:f>
-        <x:v>148</x:v>
-      </x:c>
+      <x:c r="H9" s="25" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="31" t="n">
+      <x:c r="A10" s="28" t="n">
         <x:v>46148</x:v>
       </x:c>
-      <x:c r="B10" s="26" t="str">
+      <x:c r="B10" s="25" t="str">
         <x:v>Subscriptions</x:v>
       </x:c>
-      <x:c r="C10" s="26" t="str">
+      <x:c r="C10" s="25" t="str">
         <x:v>Programėlės ir narystės</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="n">
+      <x:c r="D10" s="27" t="n">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E10" s="28" t="n">
+      <x:c r="E10" s="27" t="n">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F10" s="32" t="n">
+      <x:c r="F10" s="29" t="n">
         <x:f>D10-E10</x:f>
         <x:v>-13</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="str">
+      <x:c r="G10" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H10" s="26" t="str">
+      <x:c r="H10" s="25" t="str">
         <x:v>Patikrinti prenumeratas</x:v>
       </x:c>
-      <x:c r="J10" s="11" t="str">
-        <x:v>Subscriptions</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J10,$E$6:$E$25)</x:f>
-        <x:v>68</x:v>
-      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="31" t="n">
+      <x:c r="A11" s="28" t="n">
         <x:v>46152</x:v>
       </x:c>
-      <x:c r="B11" s="26" t="str">
+      <x:c r="B11" s="25" t="str">
         <x:v>Health</x:v>
       </x:c>
-      <x:c r="C11" s="26" t="str">
+      <x:c r="C11" s="25" t="str">
         <x:v>Vaistinė</x:v>
       </x:c>
-      <x:c r="D11" s="28" t="n">
+      <x:c r="D11" s="27" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="n">
+      <x:c r="E11" s="27" t="n">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F11" s="32" t="n">
+      <x:c r="F11" s="29" t="n">
         <x:f>D11-E11</x:f>
         <x:v>25</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="str">
+      <x:c r="G11" s="25" t="str">
         <x:v>Essential</x:v>
       </x:c>
-      <x:c r="H11" s="26" t="str"/>
-      <x:c r="J11" s="11" t="str">
-        <x:v>Health</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J11,$E$6:$E$25)</x:f>
-        <x:v>45</x:v>
-      </x:c>
+      <x:c r="H11" s="25" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="31" t="n">
+      <x:c r="A12" s="28" t="n">
         <x:v>46154</x:v>
       </x:c>
-      <x:c r="B12" s="26" t="str">
+      <x:c r="B12" s="25" t="str">
         <x:v>Education</x:v>
       </x:c>
-      <x:c r="C12" s="26" t="str">
+      <x:c r="C12" s="25" t="str">
         <x:v>Kursas</x:v>
       </x:c>
-      <x:c r="D12" s="28" t="n">
+      <x:c r="D12" s="27" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E12" s="28" t="n">
+      <x:c r="E12" s="27" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="F12" s="32" t="n">
+      <x:c r="F12" s="29" t="n">
         <x:f>D12-E12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="26" t="str">
+      <x:c r="G12" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H12" s="26" t="str"/>
-      <x:c r="J12" s="11" t="str">
-        <x:v>Education</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J12,$E$6:$E$25)</x:f>
-        <x:v>90</x:v>
-      </x:c>
+      <x:c r="H12" s="25" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="31" t="n">
+      <x:c r="A13" s="28" t="n">
         <x:v>46156</x:v>
       </x:c>
-      <x:c r="B13" s="26" t="str">
+      <x:c r="B13" s="25" t="str">
         <x:v>Entertainment</x:v>
       </x:c>
-      <x:c r="C13" s="26" t="str">
+      <x:c r="C13" s="25" t="str">
         <x:v>Kinas ir kavinės</x:v>
       </x:c>
-      <x:c r="D13" s="28" t="n">
+      <x:c r="D13" s="27" t="n">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="n">
+      <x:c r="E13" s="27" t="n">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="F13" s="32" t="n">
+      <x:c r="F13" s="29" t="n">
         <x:f>D13-E13</x:f>
         <x:v>-35</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="str">
+      <x:c r="G13" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H13" s="26" t="str">
+      <x:c r="H13" s="25" t="str">
         <x:v>Lengva sumažinti</x:v>
       </x:c>
-      <x:c r="J13" s="11" t="str">
-        <x:v>Entertainment</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J13,$E$6:$E$25)</x:f>
-        <x:v>165</x:v>
-      </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="31" t="n">
+      <x:c r="A14" s="28" t="n">
         <x:v>46160</x:v>
       </x:c>
-      <x:c r="B14" s="26" t="str">
+      <x:c r="B14" s="25" t="str">
         <x:v>Shopping</x:v>
       </x:c>
-      <x:c r="C14" s="26" t="str">
+      <x:c r="C14" s="25" t="str">
         <x:v>Drabužiai</x:v>
       </x:c>
-      <x:c r="D14" s="28" t="n">
+      <x:c r="D14" s="27" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="E14" s="28" t="n">
+      <x:c r="E14" s="27" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="F14" s="32" t="n">
+      <x:c r="F14" s="29" t="n">
         <x:f>D14-E14</x:f>
         <x:v>-60</x:v>
       </x:c>
-      <x:c r="G14" s="26" t="str">
+      <x:c r="G14" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H14" s="26" t="str">
+      <x:c r="H14" s="25" t="str">
         <x:v>Didžiausias nukrypimas</x:v>
       </x:c>
-      <x:c r="J14" s="11" t="str">
-        <x:v>Shopping</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J14,$E$6:$E$25)</x:f>
-        <x:v>210</x:v>
-      </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="31" t="n">
+      <x:c r="A15" s="28" t="n">
         <x:v>46164</x:v>
       </x:c>
-      <x:c r="B15" s="26" t="str">
+      <x:c r="B15" s="25" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="C15" s="26" t="str">
+      <x:c r="C15" s="25" t="str">
         <x:v>Dovanos</x:v>
       </x:c>
-      <x:c r="D15" s="28" t="n">
+      <x:c r="D15" s="27" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E15" s="28" t="n">
+      <x:c r="E15" s="27" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F15" s="32" t="n">
+      <x:c r="F15" s="29" t="n">
         <x:f>D15-E15</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="str">
+      <x:c r="G15" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H15" s="26" t="str"/>
-      <x:c r="J15" s="11" t="str">
+      <x:c r="H15" s="25" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="28"/>
+      <x:c r="B16" s="25" t="str">
+        <x:v>Housing</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="str"/>
+      <x:c r="D16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="29" t="n">
+        <x:f>D16-E16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="25" t="str">
+        <x:v>Essential</x:v>
+      </x:c>
+      <x:c r="H16" s="25" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="28"/>
+      <x:c r="B17" s="25" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="str"/>
+      <x:c r="D17" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="29" t="n">
+        <x:f>D17-E17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="25" t="str">
+        <x:v>Essential</x:v>
+      </x:c>
+      <x:c r="H17" s="25" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="28"/>
+      <x:c r="B18" s="25" t="str">
+        <x:v>Transport</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="str"/>
+      <x:c r="D18" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="29" t="n">
+        <x:f>D18-E18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="25" t="str">
+        <x:v>Essential</x:v>
+      </x:c>
+      <x:c r="H18" s="25" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="28"/>
+      <x:c r="B19" s="25" t="str">
+        <x:v>Utilities</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="str"/>
+      <x:c r="D19" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="29" t="n">
+        <x:f>D19-E19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="25" t="str">
+        <x:v>Essential</x:v>
+      </x:c>
+      <x:c r="H19" s="25" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="28"/>
+      <x:c r="B20" s="25" t="str">
+        <x:v>Subscriptions</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="str"/>
+      <x:c r="D20" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="29" t="n">
+        <x:f>D20-E20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="25" t="str">
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H20" s="25" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="28"/>
+      <x:c r="B21" s="25" t="str">
+        <x:v>Health</x:v>
+      </x:c>
+      <x:c r="C21" s="25" t="str"/>
+      <x:c r="D21" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="29" t="n">
+        <x:f>D21-E21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="25" t="str">
+        <x:v>Essential</x:v>
+      </x:c>
+      <x:c r="H21" s="25" t="str"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="28"/>
+      <x:c r="B22" s="25" t="str">
+        <x:v>Education</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="str"/>
+      <x:c r="D22" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="29" t="n">
+        <x:f>D22-E22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="25" t="str">
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H22" s="25" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="28"/>
+      <x:c r="B23" s="25" t="str">
+        <x:v>Entertainment</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="str"/>
+      <x:c r="D23" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F23" s="29" t="n">
+        <x:f>D23-E23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="25" t="str">
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H23" s="25" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="28"/>
+      <x:c r="B24" s="25" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="C24" s="25" t="str"/>
+      <x:c r="D24" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="29" t="n">
+        <x:f>D24-E24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="25" t="str">
+        <x:v>Optional</x:v>
+      </x:c>
+      <x:c r="H24" s="25" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="28"/>
+      <x:c r="B25" s="25" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>SUMIF($B$6:$B$25,J15,$E$6:$E$25)</x:f>
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="31"/>
-      <x:c r="B16" s="26" t="str">
-        <x:v>Housing</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="str"/>
-      <x:c r="D16" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E16" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:f>D16-E16</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="26" t="str">
-        <x:v>Essential</x:v>
-      </x:c>
-      <x:c r="H16" s="26" t="str"/>
-      <x:c r="J16" s="11"/>
-      <x:c r="K16" s="32"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="31"/>
-      <x:c r="B17" s="26" t="str">
-        <x:v>Food</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="str"/>
-      <x:c r="D17" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E17" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:f>D17-E17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="26" t="str">
-        <x:v>Essential</x:v>
-      </x:c>
-      <x:c r="H17" s="26" t="str"/>
-      <x:c r="J17" s="11" t="str">
-        <x:v>Optional spending total</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>SUMIF($G$6:$G$25,"Optional",$E$6:$E$25)</x:f>
-        <x:v>603</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="31"/>
-      <x:c r="B18" s="26" t="str">
-        <x:v>Transport</x:v>
-      </x:c>
-      <x:c r="C18" s="26" t="str"/>
-      <x:c r="D18" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E18" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:f>D18-E18</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="26" t="str">
-        <x:v>Essential</x:v>
-      </x:c>
-      <x:c r="H18" s="26" t="str"/>
-      <x:c r="J18" s="11" t="str">
-        <x:v>Essential spending total</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>SUMIF($G$6:$G$25,"Essential",$E$6:$E$25)</x:f>
-        <x:v>1608</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="31"/>
-      <x:c r="B19" s="26" t="str">
-        <x:v>Utilities</x:v>
-      </x:c>
-      <x:c r="C19" s="26" t="str"/>
-      <x:c r="D19" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E19" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:f>D19-E19</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="26" t="str">
-        <x:v>Essential</x:v>
-      </x:c>
-      <x:c r="H19" s="26" t="str"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="31"/>
-      <x:c r="B20" s="26" t="str">
-        <x:v>Subscriptions</x:v>
-      </x:c>
-      <x:c r="C20" s="26" t="str"/>
-      <x:c r="D20" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E20" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:f>D20-E20</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="26" t="str">
+      <x:c r="C25" s="25" t="str"/>
+      <x:c r="D25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="29" t="n">
+        <x:f>D25-E25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="25" t="str">
         <x:v>Optional</x:v>
       </x:c>
-      <x:c r="H20" s="26" t="str"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="31"/>
-      <x:c r="B21" s="26" t="str">
-        <x:v>Health</x:v>
-      </x:c>
-      <x:c r="C21" s="26" t="str"/>
-      <x:c r="D21" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E21" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:f>D21-E21</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="26" t="str">
-        <x:v>Essential</x:v>
-      </x:c>
-      <x:c r="H21" s="26" t="str"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="31"/>
-      <x:c r="B22" s="26" t="str">
-        <x:v>Education</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="str"/>
-      <x:c r="D22" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E22" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:f>D22-E22</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="26" t="str">
-        <x:v>Optional</x:v>
-      </x:c>
-      <x:c r="H22" s="26" t="str"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="31"/>
-      <x:c r="B23" s="26" t="str">
-        <x:v>Entertainment</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="str"/>
-      <x:c r="D23" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E23" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:f>D23-E23</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="26" t="str">
-        <x:v>Optional</x:v>
-      </x:c>
-      <x:c r="H23" s="26" t="str"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="31"/>
-      <x:c r="B24" s="26" t="str">
-        <x:v>Shopping</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="str"/>
-      <x:c r="D24" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E24" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:f>D24-E24</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="26" t="str">
-        <x:v>Optional</x:v>
-      </x:c>
-      <x:c r="H24" s="26" t="str"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="31"/>
-      <x:c r="B25" s="26" t="str">
-        <x:v>Other</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="str"/>
-      <x:c r="D25" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E25" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:f>D25-E25</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="26" t="str">
-        <x:v>Optional</x:v>
-      </x:c>
-      <x:c r="H25" s="26" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="23" t="str">
+      <x:c r="H25" s="25" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="28"/>
+      <x:c r="B26" s="25" t="str"/>
+      <x:c r="C26" s="25" t="str"/>
+      <x:c r="D26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F26" s="29" t="n">
+        <x:f>D26-E26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="25" t="str"/>
+      <x:c r="H26" s="25" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="28"/>
+      <x:c r="B27" s="25" t="str"/>
+      <x:c r="C27" s="25" t="str"/>
+      <x:c r="D27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="29" t="n">
+        <x:f>D27-E27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" s="25" t="str"/>
+      <x:c r="H27" s="25" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="17" t="str">
         <x:v>Summary</x:v>
       </x:c>
-      <x:c r="B28" s="23" t="str"/>
-      <x:c r="C28" s="23" t="str"/>
-      <x:c r="D28" s="37" t="n">
-        <x:f>SUM(D6:D25)</x:f>
+      <x:c r="B30" s="17" t="str"/>
+      <x:c r="C30" s="17" t="str"/>
+      <x:c r="D30" s="17" t="str">
+        <x:v>Total planned expenses</x:v>
+      </x:c>
+      <x:c r="E30" s="17" t="str">
+        <x:v>Total actual expenses</x:v>
+      </x:c>
+      <x:c r="F30" s="17" t="str">
+        <x:v>Expense variance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="B31" t="str"/>
+      <x:c r="C31" t="str"/>
+      <x:c r="D31" s="33" t="n">
+        <x:f>SUM(D6:D27)</x:f>
         <x:v>2125</x:v>
       </x:c>
-      <x:c r="E28" s="37" t="n">
-        <x:f>SUM(E6:E25)</x:f>
+      <x:c r="E31" s="33" t="n">
+        <x:f>SUM(E6:E27)</x:f>
         <x:v>2211</x:v>
       </x:c>
-      <x:c r="F28" s="37" t="n">
-        <x:f>D28-E28</x:f>
+      <x:c r="F31" s="33" t="n">
+        <x:f>D31-E31</x:f>
         <x:v>-86</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1859,7 +1887,7 @@
     <x:col min="4" max="4" width="22.209999084472656" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="20.860000610351562" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16.81999969482422" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.860000610351562" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22.209999084472656" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1887,208 +1915,259 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Taupymo tikslai, progresas ir statusai.</x:v>
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Tikslai, likusi suma, progresas ir statusas.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="24" t="str">
+      <x:c r="A5" s="16" t="str">
         <x:v>Goal Name</x:v>
       </x:c>
-      <x:c r="B5" s="24" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>Target Amount</x:v>
       </x:c>
-      <x:c r="C5" s="24" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>Current Saved</x:v>
       </x:c>
-      <x:c r="D5" s="24" t="str">
+      <x:c r="D5" s="16" t="str">
         <x:v>Monthly Contribution</x:v>
       </x:c>
-      <x:c r="E5" s="24" t="str">
+      <x:c r="E5" s="16" t="str">
         <x:v>Remaining Amount</x:v>
       </x:c>
-      <x:c r="F5" s="24" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>Progress %</x:v>
       </x:c>
-      <x:c r="G5" s="24" t="str">
+      <x:c r="G5" s="16" t="str">
         <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="26" t="str">
+      <x:c r="A6" s="25" t="str">
         <x:v>Emergency fund</x:v>
       </x:c>
-      <x:c r="B6" s="28" t="n">
+      <x:c r="B6" s="27" t="n">
         <x:v>3000</x:v>
       </x:c>
-      <x:c r="C6" s="28" t="n">
+      <x:c r="C6" s="27" t="n">
         <x:v>1100</x:v>
       </x:c>
-      <x:c r="D6" s="28" t="n">
+      <x:c r="D6" s="27" t="n">
         <x:v>250</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="n">
+      <x:c r="E6" s="29" t="n">
         <x:f>MAX(B6-C6,0)</x:f>
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="F6" s="39" t="n">
+      <x:c r="F6" s="35" t="n">
         <x:f>IFERROR(C6/B6,0)</x:f>
         <x:v>0.36666666666666664</x:v>
       </x:c>
-      <x:c r="G6" s="30" t="str">
+      <x:c r="G6" s="19" t="str">
         <x:f>IF(F6&gt;=1,"Goal reached",IF(D6&gt;=E6/6,"On track","Needs attention"))</x:f>
         <x:v>Needs attention</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="26" t="str">
+      <x:c r="A7" s="25" t="str">
         <x:v>Kelionė</x:v>
       </x:c>
-      <x:c r="B7" s="28" t="n">
+      <x:c r="B7" s="27" t="n">
         <x:v>1800</x:v>
       </x:c>
-      <x:c r="C7" s="28" t="n">
+      <x:c r="C7" s="27" t="n">
         <x:v>640</x:v>
       </x:c>
-      <x:c r="D7" s="28" t="n">
+      <x:c r="D7" s="27" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="E7" s="32" t="n">
+      <x:c r="E7" s="29" t="n">
         <x:f>MAX(B7-C7,0)</x:f>
         <x:v>1160</x:v>
       </x:c>
-      <x:c r="F7" s="39" t="n">
+      <x:c r="F7" s="35" t="n">
         <x:f>IFERROR(C7/B7,0)</x:f>
         <x:v>0.35555555555555557</x:v>
       </x:c>
-      <x:c r="G7" s="30" t="str">
+      <x:c r="G7" s="19" t="str">
         <x:f>IF(F7&gt;=1,"Goal reached",IF(D7&gt;=E7/6,"On track","Needs attention"))</x:f>
         <x:v>Needs attention</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="26" t="str">
+      <x:c r="A8" s="25" t="str">
         <x:v>Investavimo pradžia</x:v>
       </x:c>
-      <x:c r="B8" s="28" t="n">
+      <x:c r="B8" s="27" t="n">
         <x:v>1200</x:v>
       </x:c>
-      <x:c r="C8" s="28" t="n">
+      <x:c r="C8" s="27" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="D8" s="28" t="n">
+      <x:c r="D8" s="27" t="n">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="n">
+      <x:c r="E8" s="29" t="n">
         <x:f>MAX(B8-C8,0)</x:f>
         <x:v>900</x:v>
       </x:c>
-      <x:c r="F8" s="39" t="n">
+      <x:c r="F8" s="35" t="n">
         <x:f>IFERROR(C8/B8,0)</x:f>
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="str">
+      <x:c r="G8" s="19" t="str">
         <x:f>IF(F8&gt;=1,"Goal reached",IF(D8&gt;=E8/6,"On track","Needs attention"))</x:f>
         <x:v>Needs attention</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="26" t="str">
+      <x:c r="A9" s="25" t="str">
         <x:v>Namų atnaujinimas</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="n">
+      <x:c r="B9" s="27" t="n">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="n">
+      <x:c r="C9" s="27" t="n">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="n">
+      <x:c r="D9" s="27" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E9" s="32" t="n">
+      <x:c r="E9" s="29" t="n">
         <x:f>MAX(B9-C9,0)</x:f>
         <x:v>680</x:v>
       </x:c>
-      <x:c r="F9" s="39" t="n">
+      <x:c r="F9" s="35" t="n">
         <x:f>IFERROR(C9/B9,0)</x:f>
         <x:v>0.24444444444444444</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="str">
+      <x:c r="G9" s="19" t="str">
         <x:f>IF(F9&gt;=1,"Goal reached",IF(D9&gt;=E9/6,"On track","Needs attention"))</x:f>
         <x:v>Needs attention</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="26" t="str">
+      <x:c r="A10" s="25" t="str">
         <x:v>Mokymosi fondas</x:v>
       </x:c>
-      <x:c r="B10" s="28" t="n">
+      <x:c r="B10" s="27" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="C10" s="28" t="n">
+      <x:c r="C10" s="27" t="n">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="D10" s="28" t="n">
+      <x:c r="D10" s="27" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E10" s="32" t="n">
+      <x:c r="E10" s="29" t="n">
         <x:f>MAX(B10-C10,0)</x:f>
         <x:v>420</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="35" t="n">
         <x:f>IFERROR(C10/B10,0)</x:f>
         <x:v>0.3</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="str">
+      <x:c r="G10" s="19" t="str">
         <x:f>IF(F10&gt;=1,"Goal reached",IF(D10&gt;=E10/6,"On track","Needs attention"))</x:f>
         <x:v>Needs attention</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="26" t="str"/>
-      <x:c r="B11" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C11" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="32" t="n">
+      <x:c r="A11" s="25" t="str"/>
+      <x:c r="B11" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C11" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="29" t="n">
         <x:f>MAX(B11-C11,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="39" t="n">
+      <x:c r="F11" s="35" t="n">
         <x:f>IFERROR(C11/B11,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="str">
+      <x:c r="G11" s="19" t="str">
         <x:f>IF(F11&gt;=1,"Goal reached",IF(D11&gt;=E11/6,"On track","Needs attention"))</x:f>
+        <x:v>On track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="25" t="str"/>
+      <x:c r="B12" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="29" t="n">
+        <x:f>MAX(B12-C12,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="35" t="n">
+        <x:f>IFERROR(C12/B12,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="19" t="str">
+        <x:f>IF(F12&gt;=1,"Goal reached",IF(D12&gt;=E12/6,"On track","Needs attention"))</x:f>
+        <x:v>On track</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="25" t="str"/>
+      <x:c r="B13" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="29" t="n">
+        <x:f>MAX(B13-C13,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="35" t="n">
+        <x:f>IFERROR(C13/B13,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="19" t="str">
+        <x:f>IF(F13&gt;=1,"Goal reached",IF(D13&gt;=E13/6,"On track","Needs attention"))</x:f>
         <x:v>On track</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2098,132 +2177,387 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.940000534057617" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="69.30999755859375" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="23.549999237060547" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="23.549999237060547" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="23.549999237060547" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.81999969482422" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22.209999084472656" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>Monthly Review</x:v>
+        <x:v>Category Summary</x:v>
       </x:c>
       <x:c r="B1" s="5" t="str">
-        <x:v>Monthly Review</x:v>
+        <x:v>Category Summary</x:v>
       </x:c>
       <x:c r="C1" s="5" t="str">
-        <x:v>Monthly Review</x:v>
+        <x:v>Category Summary</x:v>
       </x:c>
       <x:c r="D1" s="5" t="str">
-        <x:v>Monthly Review</x:v>
+        <x:v>Category Summary</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="str">
+        <x:v>Category Summary</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="str">
+        <x:v>Category Summary</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Mėnesio peržiūra, sprendimai ir kiti veiksmai.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="24" t="str">
-        <x:v>Klausimas</x:v>
-      </x:c>
-      <x:c r="B4" s="24" t="str">
-        <x:v>Atsakymas</x:v>
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Automatinė išlaidų kategorijų analizė.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Monthly wins</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>Pavyko išlaikyti būsto ir transporto išlaidas pagal planą.</x:v>
+      <x:c r="A5" s="16" t="str">
+        <x:v>Category</x:v>
+      </x:c>
+      <x:c r="B5" s="16" t="str">
+        <x:v>Planned Total</x:v>
+      </x:c>
+      <x:c r="C5" s="16" t="str">
+        <x:v>Actual Total</x:v>
+      </x:c>
+      <x:c r="D5" s="16" t="str">
+        <x:v>Difference</x:v>
+      </x:c>
+      <x:c r="E5" s="16" t="str">
+        <x:v>% of Total Spending</x:v>
+      </x:c>
+      <x:c r="F5" s="16" t="str">
+        <x:v>Status</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Biggest expense</x:v>
-      </x:c>
-      <x:c r="B6" s="30" t="n">
-        <x:f>Dashboard!B12</x:f>
+      <x:c r="A6" s="10" t="str">
+        <x:v>Housing</x:v>
+      </x:c>
+      <x:c r="B6" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A6,Expenses!$D$6:$D$27)</x:f>
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="C6" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A6,Expenses!$E$6:$E$27)</x:f>
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="D6" s="29" t="n">
+        <x:f>B6-C6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="35" t="n">
+        <x:f>IFERROR(C6/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.38444142921754865</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="str">
+        <x:f>IF(C6=0,"No data",IF(D6&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A7,Expenses!$D$6:$D$27)</x:f>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A7,Expenses!$E$6:$E$27)</x:f>
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="D7" s="29" t="n">
+        <x:f>B7-C7</x:f>
+        <x:v>-35</x:v>
+      </x:c>
+      <x:c r="E7" s="35" t="n">
+        <x:f>IFERROR(C7/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.20578923563998192</x:v>
+      </x:c>
+      <x:c r="F7" s="19" t="str">
+        <x:f>IF(C7=0,"No data",IF(D7&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>Over plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>Transport</x:v>
+      </x:c>
+      <x:c r="B8" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A8,Expenses!$D$6:$D$27)</x:f>
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C8" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A8,Expenses!$E$6:$E$27)</x:f>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D8" s="29" t="n">
+        <x:f>B8-C8</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="35" t="n">
+        <x:f>IFERROR(C8/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.04975124378109453</x:v>
+      </x:c>
+      <x:c r="F8" s="19" t="str">
+        <x:f>IF(C8=0,"No data",IF(D8&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>Utilities</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A9,Expenses!$D$6:$D$27)</x:f>
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="C9" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A9,Expenses!$E$6:$E$27)</x:f>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="D9" s="29" t="n">
+        <x:f>B9-C9</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E9" s="35" t="n">
+        <x:f>IFERROR(C9/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.06693803708729082</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="str">
+        <x:f>IF(C9=0,"No data",IF(D9&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>Subscriptions</x:v>
+      </x:c>
+      <x:c r="B10" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A10,Expenses!$D$6:$D$27)</x:f>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C10" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A10,Expenses!$E$6:$E$27)</x:f>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D10" s="29" t="n">
+        <x:f>B10-C10</x:f>
+        <x:v>-13</x:v>
+      </x:c>
+      <x:c r="E10" s="35" t="n">
+        <x:f>IFERROR(C10/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.03075531433740389</x:v>
+      </x:c>
+      <x:c r="F10" s="19" t="str">
+        <x:f>IF(C10=0,"No data",IF(D10&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>Over plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="10" t="str">
+        <x:v>Health</x:v>
+      </x:c>
+      <x:c r="B11" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A11,Expenses!$D$6:$D$27)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C11" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A11,Expenses!$E$6:$E$27)</x:f>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D11" s="29" t="n">
+        <x:f>B11-C11</x:f>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="35" t="n">
+        <x:f>IFERROR(C11/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.0203527815468114</x:v>
+      </x:c>
+      <x:c r="F11" s="19" t="str">
+        <x:f>IF(C11=0,"No data",IF(D11&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="10" t="str">
+        <x:v>Education</x:v>
+      </x:c>
+      <x:c r="B12" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A12,Expenses!$D$6:$D$27)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C12" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A12,Expenses!$E$6:$E$27)</x:f>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D12" s="29" t="n">
+        <x:f>B12-C12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="35" t="n">
+        <x:f>IFERROR(C12/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.0407055630936228</x:v>
+      </x:c>
+      <x:c r="F12" s="19" t="str">
+        <x:f>IF(C12=0,"No data",IF(D12&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="10" t="str">
+        <x:v>Entertainment</x:v>
+      </x:c>
+      <x:c r="B13" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A13,Expenses!$D$6:$D$27)</x:f>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C13" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A13,Expenses!$E$6:$E$27)</x:f>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="D13" s="29" t="n">
+        <x:f>B13-C13</x:f>
+        <x:v>-35</x:v>
+      </x:c>
+      <x:c r="E13" s="35" t="n">
+        <x:f>IFERROR(C13/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.07462686567164178</x:v>
+      </x:c>
+      <x:c r="F13" s="19" t="str">
+        <x:f>IF(C13=0,"No data",IF(D13&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>Over plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="B14" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A14,Expenses!$D$6:$D$27)</x:f>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C14" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A14,Expenses!$E$6:$E$27)</x:f>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="D14" s="29" t="n">
+        <x:f>B14-C14</x:f>
+        <x:v>-60</x:v>
+      </x:c>
+      <x:c r="E14" s="35" t="n">
+        <x:f>IFERROR(C14/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.09497964721845319</x:v>
+      </x:c>
+      <x:c r="F14" s="19" t="str">
+        <x:f>IF(C14=0,"No data",IF(D14&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>Over plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B15" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A15,Expenses!$D$6:$D$27)</x:f>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C15" s="29" t="n">
+        <x:f>SUMIF(Expenses!$B$6:$B$27,A15,Expenses!$E$6:$E$27)</x:f>
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D15" s="29" t="n">
+        <x:f>B15-C15</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E15" s="35" t="n">
+        <x:f>IFERROR(C15/SUM($C$6:$C$15),0)</x:f>
+        <x:v>0.031659882406151064</x:v>
+      </x:c>
+      <x:c r="F15" s="19" t="str">
+        <x:f>IF(C15=0,"No data",IF(D15&gt;=0,"On plan","Over plan"))</x:f>
+        <x:v>On plan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10"/>
+      <x:c r="B16" s="29"/>
+      <x:c r="C16" s="29"/>
+      <x:c r="D16" s="29"/>
+      <x:c r="E16" s="19"/>
+      <x:c r="F16" s="19"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>Summary</x:v>
+      </x:c>
+      <x:c r="B17" s="29" t="str">
+        <x:v>Average spending per category</x:v>
+      </x:c>
+      <x:c r="C17" s="29" t="str">
+        <x:v>Largest category amount</x:v>
+      </x:c>
+      <x:c r="D17" s="29" t="str">
+        <x:v>Categories over plan</x:v>
+      </x:c>
+      <x:c r="E17" s="19" t="str">
+        <x:v>Optional spending</x:v>
+      </x:c>
+      <x:c r="F17" s="19" t="str">
+        <x:v>Essential spending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>Formula output</x:v>
+      </x:c>
+      <x:c r="B18" s="29" t="n">
+        <x:f>AVERAGE(C6:C15)</x:f>
+        <x:v>221.1</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="n">
+        <x:f>MAX(C6:C15)</x:f>
+        <x:v>850</x:v>
+      </x:c>
+      <x:c r="D18" s="29" t="n">
+        <x:f>COUNTIF(F6:F15,"Over plan")</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E18" s="29" t="n">
+        <x:f>SUMIF(Expenses!$G$6:$G$27,"Optional",Expenses!$E$6:$E$27)</x:f>
         <x:v>603</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>Spending mistake</x:v>
-      </x:c>
-      <x:c r="B7" s="26" t="str">
-        <x:v>Pramogoms ir pirkiniams išleista daugiau nei planuota.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>Next month adjustment</x:v>
-      </x:c>
-      <x:c r="B8" s="26" t="str">
-        <x:v>Sumažinti optional išlaidas 10-15% ir peržiūrėti prenumeratas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Review date</x:v>
-      </x:c>
-      <x:c r="B9" s="31" t="n">
-        <x:v>46173</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="24" t="str">
-        <x:v>3 action steps</x:v>
-      </x:c>
-      <x:c r="B12" s="24" t="str"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B13" s="26" t="str">
-        <x:v>Atšaukti nenaudojamas prenumeratas iki kito mėnesio 5 dienos.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B14" s="26" t="str">
-        <x:v>Nustatyti savaitinį maisto biudžetą ir sekti realias išlaidas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="11" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B15" s="26" t="str">
-        <x:v>Padidinti automatinį taupymo pervedimą iki tikslo normos.</x:v>
+      <x:c r="F18" s="29" t="n">
+        <x:f>SUMIF(Expenses!$G$6:$G$27,"Essential",Expenses!$E$6:$E$27)</x:f>
+        <x:v>1608</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2233,15 +2567,161 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30.280000686645508" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23.549999237060547" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="4.710000038146973" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="30.280000686645508" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="23.549999237060547" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.710000038146973" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="19.520000457763672" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="19.520000457763672" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="39.70000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="72.01000213623047" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="23.549999237060547" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23.549999237060547" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Monthly Review</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="str">
+        <x:v>Monthly Review</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
+        <x:v>Monthly Review</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="str">
+        <x:v>Monthly Review</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="B2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="C2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="D2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="E2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="G2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>Mėnesio refleksija ir trijų veiksmų planas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="16" t="str">
+        <x:v>Klausimas</x:v>
+      </x:c>
+      <x:c r="B4" s="16" t="str">
+        <x:v>Atsakymas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="10" t="str">
+        <x:v>Kas šį mėnesį pavyko geriausiai?</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>Pajamos viršijo planą, o pagrindinės būtinos išlaidos liko stabilios.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="10" t="str">
+        <x:v>Didžiausios išlaidos</x:v>
+      </x:c>
+      <x:c r="B6" s="19" t="str">
+        <x:f>Dashboard!B13</x:f>
+        <x:v>Housing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="10" t="str">
+        <x:v>Nebūtinos išlaidos, kurias galima mažinti</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>Pramogos, pirkiniai ir nenaudojamos prenumeratos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="10" t="str">
+        <x:v>Didžiausias finansinis laimėjimas</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>Mėnesio balansas liko teigiamas ir viršijo taupymo tikslą.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>Ką koreguoti kitą mėnesį?</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="str">
+        <x:v>Mažinti optional išlaidas ir iš anksto suplanuoti pirkinius.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="10" t="str">
+        <x:v>Review date</x:v>
+      </x:c>
+      <x:c r="B10" s="28" t="n">
+        <x:v>46173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="16" t="str">
+        <x:v>3 veiksmai kitam mėnesiui</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="10" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="25" t="str">
+        <x:v>Atšaukti nenaudojamas prenumeratas iki kito mėnesio 5 dienos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="10" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="25" t="str">
+        <x:v>Nustatyti savaitinį maisto ir pramogų limitą.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="10" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="25" t="str">
+        <x:v>Padidinti automatinį taupymo pervedimą iki tikslinės normos.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:H2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="32.970001220703125" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.9000000953674316" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="32.970001220703125" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="3.9000000953674316" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.860000610351562" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20.860000610351562" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20.860000610351562" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2275,234 +2755,278 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="C2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="E2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="F2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
       <x:c r="G2" s="7" t="str">
-        <x:v>Automatinė biudžeto apžvalga pagal Income, Expenses ir Savings Goals lapus.</x:v>
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
+      </x:c>
+      <x:c r="H2" s="7" t="str">
+        <x:v>V16 automatinė biudžeto apžvalga, sveikatos balas ir rekomendacijos.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="24" t="str">
+      <x:c r="A4" s="16" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="B4" s="24" t="str">
+      <x:c r="B4" s="16" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="D4" s="24" t="str">
-        <x:v>Quick view</x:v>
-      </x:c>
-      <x:c r="E4" s="24" t="str">
-        <x:v>Result</x:v>
-      </x:c>
-      <x:c r="G4" s="24" t="str">
+      <x:c r="D4" s="16" t="str">
+        <x:v>Profile</x:v>
+      </x:c>
+      <x:c r="E4" s="16" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="G4" s="16" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="H4" s="24" t="str">
+      <x:c r="H4" s="16" t="str">
         <x:v>Planned</x:v>
       </x:c>
-      <x:c r="I4" s="24" t="str">
+      <x:c r="I4" s="16" t="str">
         <x:v>Actual</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="10" t="str">
         <x:v>Total actual income</x:v>
       </x:c>
-      <x:c r="B5" s="32" t="n">
-        <x:f>Income!E18</x:f>
+      <x:c r="B5" s="29" t="n">
+        <x:f>Income!E21</x:f>
         <x:v>3015</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>Mėnuo</x:v>
-      </x:c>
-      <x:c r="E5" s="30" t="str">
+      <x:c r="D5" s="10" t="str">
+        <x:v>Month</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="str">
         <x:f>Inputs!B5</x:f>
         <x:v>2026 gegužė</x:v>
       </x:c>
-      <x:c r="G5" s="11" t="str">
+      <x:c r="G5" s="10" t="str">
         <x:v>Income</x:v>
       </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>Income!D18</x:f>
+      <x:c r="H5" s="29" t="n">
+        <x:f>Income!D21</x:f>
         <x:v>2920</x:v>
       </x:c>
-      <x:c r="I5" s="32" t="n">
-        <x:f>Income!E18</x:f>
+      <x:c r="I5" s="29" t="n">
+        <x:f>Income!E21</x:f>
         <x:v>3015</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="10" t="str">
         <x:v>Total actual expenses</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="n">
-        <x:f>Expenses!E28</x:f>
+      <x:c r="B6" s="29" t="n">
+        <x:f>Expenses!E31</x:f>
         <x:v>2211</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>Valiuta</x:v>
-      </x:c>
-      <x:c r="E6" s="30" t="str">
+      <x:c r="D6" s="10" t="str">
+        <x:v>Currency</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="str">
         <x:f>Inputs!B6</x:f>
         <x:v>€</x:v>
       </x:c>
-      <x:c r="G6" s="11" t="str">
+      <x:c r="G6" s="10" t="str">
         <x:v>Expenses</x:v>
       </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>Expenses!D28</x:f>
+      <x:c r="H6" s="29" t="n">
+        <x:f>Expenses!D31</x:f>
         <x:v>2125</x:v>
       </x:c>
-      <x:c r="I6" s="32" t="n">
-        <x:f>Expenses!E28</x:f>
+      <x:c r="I6" s="29" t="n">
+        <x:f>Expenses!E31</x:f>
         <x:v>2211</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="10" t="str">
         <x:v>Monthly balance</x:v>
       </x:c>
-      <x:c r="B7" s="32" t="n">
+      <x:c r="B7" s="29" t="n">
         <x:f>B5-B6</x:f>
         <x:v>804</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>Taupymo tikslas</x:v>
-      </x:c>
-      <x:c r="E7" s="43" t="n">
+      <x:c r="D7" s="10" t="str">
+        <x:v>User / household</x:v>
+      </x:c>
+      <x:c r="E7" s="19" t="str">
         <x:f>Inputs!B7</x:f>
-        <x:v>0.2</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="str">
+        <x:v>StillOak šeima</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="str">
         <x:v>Balance</x:v>
       </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>Income!D18-Expenses!D28</x:f>
+      <x:c r="H7" s="29" t="n">
+        <x:f>Income!D21-Expenses!D31</x:f>
         <x:v>795</x:v>
       </x:c>
-      <x:c r="I7" s="32" t="n">
-        <x:f>Income!E18-Expenses!E28</x:f>
+      <x:c r="I7" s="29" t="n">
+        <x:f>Income!E21-Expenses!E31</x:f>
         <x:v>804</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="10" t="str">
         <x:v>Savings rate %</x:v>
       </x:c>
-      <x:c r="B8" s="39" t="n">
+      <x:c r="B8" s="35" t="n">
         <x:f>IFERROR(B7/B5,0)</x:f>
         <x:v>0.26666666666666666</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>Emergency fund goal</x:v>
-      </x:c>
-      <x:c r="E8" s="32" t="n">
+      <x:c r="D8" s="10" t="str">
+        <x:v>Savings target</x:v>
+      </x:c>
+      <x:c r="E8" s="40" t="n">
         <x:f>Inputs!B8</x:f>
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="10" t="str">
+        <x:v>Planned vs actual income</x:v>
+      </x:c>
+      <x:c r="B9" s="29" t="n">
+        <x:f>Income!E21-Income!D21</x:f>
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D9" s="10" t="str">
+        <x:v>Emergency fund target</x:v>
+      </x:c>
+      <x:c r="E9" s="29" t="n">
+        <x:f>Inputs!B9</x:f>
         <x:v>3000</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Planned vs actual income</x:v>
-      </x:c>
-      <x:c r="B9" s="32" t="n">
-        <x:f>Income!E18-Income!D18</x:f>
-        <x:v>95</x:v>
-      </x:c>
-    </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
+      <x:c r="A10" s="10" t="str">
         <x:v>Planned vs actual expenses</x:v>
       </x:c>
-      <x:c r="B10" s="32" t="n">
-        <x:f>Expenses!E28-Expenses!D28</x:f>
+      <x:c r="B10" s="29" t="n">
+        <x:f>Expenses!E31-Expenses!D31</x:f>
         <x:v>86</x:v>
       </x:c>
+      <x:c r="D10" s="10" t="str">
+        <x:v>Monthly note</x:v>
+      </x:c>
+      <x:c r="E10" s="19" t="str">
+        <x:f>Inputs!B10</x:f>
+        <x:v>Pavyzdinis mėnuo su papildomomis pajamomis ir keliomis optional išlaidomis.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
+      <x:c r="A11" s="10" t="str">
         <x:v>Essential expenses</x:v>
       </x:c>
-      <x:c r="B11" s="32" t="n">
-        <x:f>Expenses!K18</x:f>
+      <x:c r="B11" s="29" t="n">
+        <x:f>'Category Summary'!F18</x:f>
         <x:v>1608</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="str">
+      <x:c r="A12" s="10" t="str">
         <x:v>Optional expenses</x:v>
       </x:c>
-      <x:c r="B12" s="32" t="n">
-        <x:f>Expenses!K17</x:f>
+      <x:c r="B12" s="29" t="n">
+        <x:f>'Category Summary'!E18</x:f>
         <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11" t="str">
+      <x:c r="A13" s="10" t="str">
         <x:v>Largest expense category</x:v>
       </x:c>
-      <x:c r="B13" s="30" t="str">
-        <x:f>INDEX(Expenses!J6:J15,MATCH(MAX(Expenses!K6:K15),Expenses!K6:K15,0))</x:f>
+      <x:c r="B13" s="19" t="str">
+        <x:f>INDEX('Category Summary'!A6:A15,MATCH(MAX('Category Summary'!C6:C15),'Category Summary'!C6:C15,0))</x:f>
         <x:v>Housing</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11" t="str">
+      <x:c r="A14" s="10" t="str">
         <x:v>Emergency fund progress</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
-        <x:f>IFERROR(SUM('Savings Goals'!C6:C11)/Inputs!B8,0)</x:f>
+      <x:c r="B14" s="29" t="n">
+        <x:f>IFERROR(SUM('Savings Goals'!C6:C13)/Inputs!B9,0)</x:f>
         <x:v>0.8133333333333334</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="str">
+      <x:c r="A15" s="10" t="str">
         <x:v>Savings goal progress</x:v>
       </x:c>
-      <x:c r="B15" s="39" t="n">
-        <x:f>IFERROR(SUM('Savings Goals'!C6:C11)/SUM('Savings Goals'!B6:B11),0)</x:f>
+      <x:c r="B15" s="35" t="n">
+        <x:f>IFERROR(SUM('Savings Goals'!C6:C13)/SUM('Savings Goals'!B6:B13),0)</x:f>
         <x:v>0.3253333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11" t="str">
+      <x:c r="A16" s="10" t="str">
+        <x:v>Average spending per category</x:v>
+      </x:c>
+      <x:c r="B16" s="35" t="n">
+        <x:f>'Category Summary'!B18</x:f>
+        <x:v>221.1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="10" t="str">
+        <x:v>Optional spending ratio</x:v>
+      </x:c>
+      <x:c r="B17" s="37" t="n">
+        <x:f>IFERROR(B12/B6,0)</x:f>
+        <x:v>0.2727272727272727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="10" t="str">
+        <x:v>Budget health score</x:v>
+      </x:c>
+      <x:c r="B18" s="19" t="n">
+        <x:f>MIN(100,MAX(0,IF(B7&gt;0,25,0)+MIN(B8/20%,1)*25+(1-MIN(B17/40%,1))*25+MIN(B15,1)*25))</x:f>
+        <x:v>66.0878787878788</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="10" t="str">
         <x:v>Budget status message</x:v>
       </x:c>
-      <x:c r="B16" s="42" t="str">
+      <x:c r="B19" s="39" t="str">
         <x:f>IF(B7&lt;0,"Išlaidos viršijo pajamas – reikia mažinti išlaidas.",IF(B8&gt;=20%,"Stiprus mėnuo – taupymo norma gera.",IF(B8&gt;=10%,"Stabilus mėnuo – galima dar optimizuoti išlaidas.","Reikia peržiūrėti išlaidas ir padidinti taupymą.")))</x:f>
         <x:v>Stiprus mėnuo – taupymo norma gera.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="11" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="10" t="str">
         <x:v>Recommendation message</x:v>
       </x:c>
-      <x:c r="B17" s="42" t="str">
-        <x:f>IF(B7&lt;0,"Sumažinkite optional išlaidas ir peržiūrėkite didžiausias kategorijas.",IF(B8&gt;=Inputs!B7,"Išlaikykite ritmą ir nukreipkite perteklių į prioritetinį tikslą.","Padidinkite taupymo įnašą arba sumažinkite mažos vertės išlaidas."))</x:f>
-        <x:v>Išlaikykite ritmą ir nukreipkite perteklių į prioritetinį tikslą.</x:v>
+      <x:c r="B20" s="39" t="str">
+        <x:f>IF(B18&gt;=80,"Puiki finansinė kryptis – tęskite dabartinį planą.",IF(B18&gt;=60,"Stabilu, bet verta optimizuoti kelias išlaidų kategorijas.",IF(B18&gt;=40,"Reikia peržiūrėti išlaidas ir sustiprinti taupymo planą.","Biudžetą būtina koreguoti – pradėkite nuo nebūtinų išlaidų mažinimo.")))</x:f>
+        <x:v>Stabilu, bet verta optimizuoti kelias išlaidų kategorijas.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98db55774de54835"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a28bbb3206642ee"/>
 </x:worksheet>
 </file>